--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/EIXO GARFO_.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/EIXO GARFO_.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -480,53 +470,6 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>7899468058547</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ROLAMENT BALANÇA TRILHA XTZ125 2003 A 2014/ XTZ150 2019 A 2023/ XTZ250</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>4896061</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ROLAMENT BALANÇA NXR125-150-160/ XRE190-300/ XR250</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
     </row>
